--- a/Juande_P4y0_/Ajustes_Mapeo_K-OCurrencia.xlsx
+++ b/Juande_P4y0_/Ajustes_Mapeo_K-OCurrencia.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juandediosamate/Documents/Universidad/Curso_4_de_Fisica/GNOMOS/Juande_P4y0_/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juandediosamate/Documents/Universidad/Curso_4_de_Fisica/Electronica_Gnomos/GNOMOS/Juande_P4y0_/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0706A05A-EBD8-914B-8700-76C5D915E110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5591C4-14EA-0247-9D03-D5210B6909C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3880" yWindow="3940" windowWidth="28040" windowHeight="17440" xr2:uid="{9378BCD6-30DA-5147-A5E0-A0CF32A295BC}"/>
+    <workbookView xWindow="25160" yWindow="500" windowWidth="26060" windowHeight="26520" xr2:uid="{9378BCD6-30DA-5147-A5E0-A0CF32A295BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,6 +28,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="23">
   <si>
     <t>N</t>
   </si>
@@ -98,6 +99,12 @@
   </si>
   <si>
     <t>TERCERN GAP (K=3)</t>
+  </si>
+  <si>
+    <t>N=100</t>
+  </si>
+  <si>
+    <t>ocurrenca</t>
   </si>
 </sst>
 </file>
@@ -478,6 +485,762 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="172691040"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$I$86</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>n</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-ES"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja1!$H$87:$H$90</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>239</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>319</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja1!$I$87:$I$90</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>160</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2F6C-4245-B557-BE147D5ABA02}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="419673680"/>
+        <c:axId val="420074128"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="419673680"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="420074128"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="420074128"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="419673680"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>n</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-ES"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja1!$F$114:$F$121</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>298</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>398</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>239</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>319</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja1!$G$114:$G$121</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>160</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-237B-B940-88E6-B8D2BAD4C2C2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="465878496"/>
+        <c:axId val="456238384"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="465878496"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="456238384"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="456238384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="465878496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2871,7 +3634,813 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$E$86</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>n</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-ES"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja1!$D$87:$D$91</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>298</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>398</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja1!$E$87:$E$91</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>250</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2850-9847-AD49-08805E65BCF6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="393132736"/>
+        <c:axId val="393170016"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="393132736"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="393170016"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="393170016"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="393132736"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.32356933508311458"/>
+          <c:y val="2.7777777777777776E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-ES"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja1!$S$36:$S$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja1!$T$36:$T$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E08B-0540-839D-D1C975BD3001}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="419976800"/>
+        <c:axId val="420036000"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="419976800"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="420036000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="420036000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="419976800"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3151,6 +4720,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -3667,7 +5316,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4183,7 +5832,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4699,7 +6348,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5215,7 +6864,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5731,7 +7380,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6247,7 +7896,2071 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7017,6 +10730,150 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>630767</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>110067</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>224367</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>8467</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Gráfico 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74F8A916-4C80-8A4F-B4BE-392F5AF529A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>690033</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>283633</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Gráfico 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4A360D3-8203-4AC4-DC4D-2BD10B99F20D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>440266</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>8466</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>33866</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>110066</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="12" name="Gráfico 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D7E9BDF-202A-7414-E4C6-E66C4BCD17B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>338668</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>8466</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>762001</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>110066</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="13" name="Gráfico 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E11E685D-D891-D132-0DB8-BCF31F510A54}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7317,7 +11174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C97253E-D333-CB49-9C64-23580227EDAE}">
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:T121"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -7610,12 +11467,20 @@
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="S36">
+        <v>29</v>
+      </c>
+      <c r="T36">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C37" t="s">
         <v>17</v>
       </c>
@@ -7625,8 +11490,14 @@
       <c r="I37" t="s">
         <v>20</v>
       </c>
+      <c r="S37">
+        <v>55</v>
+      </c>
+      <c r="T37">
+        <v>30</v>
+      </c>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
         <v>0</v>
       </c>
@@ -7648,8 +11519,14 @@
       <c r="J38" t="s">
         <v>15</v>
       </c>
+      <c r="S38">
+        <v>80</v>
+      </c>
+      <c r="T38">
+        <v>45</v>
+      </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B39">
         <v>10</v>
       </c>
@@ -7675,7 +11552,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B40">
         <v>15</v>
       </c>
@@ -7701,7 +11578,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B41">
         <v>20</v>
       </c>
@@ -7727,7 +11604,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B42">
         <v>25</v>
       </c>
@@ -7753,7 +11630,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B43">
         <v>30</v>
       </c>
@@ -7897,6 +11774,179 @@
       </c>
       <c r="E78">
         <v>45</v>
+      </c>
+    </row>
+    <row r="86" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B86" t="s">
+        <v>21</v>
+      </c>
+      <c r="D86" t="s">
+        <v>6</v>
+      </c>
+      <c r="E86" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" t="s">
+        <v>6</v>
+      </c>
+      <c r="I86" t="s">
+        <v>15</v>
+      </c>
+      <c r="K86" t="s">
+        <v>6</v>
+      </c>
+      <c r="L86" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B87">
+        <v>100</v>
+      </c>
+      <c r="D87">
+        <v>99</v>
+      </c>
+      <c r="E87">
+        <f>1/2*100</f>
+        <v>50</v>
+      </c>
+      <c r="H87">
+        <v>79</v>
+      </c>
+      <c r="I87">
+        <f>1/2*80</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="88" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D88">
+        <v>199</v>
+      </c>
+      <c r="E88">
+        <f>2/2*100</f>
+        <v>100</v>
+      </c>
+      <c r="H88">
+        <v>159</v>
+      </c>
+      <c r="I88">
+        <f>2/2*80</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="89" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D89">
+        <v>298</v>
+      </c>
+      <c r="E89">
+        <f>3/2*100</f>
+        <v>150</v>
+      </c>
+      <c r="H89">
+        <v>239</v>
+      </c>
+      <c r="I89">
+        <f>3/2*80</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="90" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D90">
+        <v>398</v>
+      </c>
+      <c r="E90">
+        <f>4/2*100</f>
+        <v>200</v>
+      </c>
+      <c r="H90">
+        <v>319</v>
+      </c>
+      <c r="I90">
+        <f>4/2*80</f>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="91" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="E91">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="92" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="E92">
+        <f>6/2*100</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="113" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F113" t="s">
+        <v>22</v>
+      </c>
+      <c r="G113" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F114">
+        <v>99</v>
+      </c>
+      <c r="G114">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="115" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F115">
+        <v>199</v>
+      </c>
+      <c r="G115">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="116" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F116">
+        <v>298</v>
+      </c>
+      <c r="G116">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="117" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F117">
+        <v>398</v>
+      </c>
+      <c r="G117">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="118" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F118">
+        <v>79</v>
+      </c>
+      <c r="G118">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="119" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F119">
+        <v>159</v>
+      </c>
+      <c r="G119">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="120" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F120">
+        <v>239</v>
+      </c>
+      <c r="G120">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="121" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F121">
+        <v>319</v>
+      </c>
+      <c r="G121">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
